--- a/SYSTEM TESTING.xlsx
+++ b/SYSTEM TESTING.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ba5dca7ca716306/Desktop/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="8_{BE074D1D-68D3-4207-A388-F58B7058BB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F03D7BD7-4452-4F72-A565-FDA3F3247236}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{BE074D1D-68D3-4207-A388-F58B7058BB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9654C3D7-04D1-4E7F-8859-6C8382B53E2B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{28F2FB74-1599-4A70-9BA1-E24713E20AC2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{28F2FB74-1599-4A70-9BA1-E24713E20AC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -246,15 +246,9 @@
     <t>VERIFY USER CAN SAVE REEL</t>
   </si>
   <si>
-    <t>GO TO REELS -&gt; CLICK ON SAVE BUTTON</t>
-  </si>
-  <si>
     <t>VERIFY USER CAN SHARE REEL</t>
   </si>
   <si>
-    <t>GO TO REELS -&gt; CLICK ON SHARE -&gt; SELECT THE USER/USERS TO SHARE -&gt; SHARE</t>
-  </si>
-  <si>
     <t xml:space="preserve">VERIFY USER CAN REPOST THE REEL </t>
   </si>
   <si>
@@ -463,6 +457,12 @@
   </si>
   <si>
     <t>VERIFY USER CAN FOLLOW/UNFOLLOW</t>
+  </si>
+  <si>
+    <t>GO TO REELS -&gt; CLICK ON SAVE BUTTON -&gt; check my activity</t>
+  </si>
+  <si>
+    <t>GO TO REELS -&gt; CLICK ON SHARE -&gt; SELECT THE USER/USERS TO SHARE -&gt; SHARE -&gt; check chats section</t>
   </si>
 </sst>
 </file>
@@ -512,10 +512,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1093,10 +1092,10 @@
         <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1112,7 +1111,7 @@
   <cols>
     <col min="1" max="1" width="21.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="59.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="87.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1129,7 +1128,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C2" s="1"/>
     </row>
@@ -1171,57 +1170,57 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1296,90 +1295,90 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" t="s">
         <v>108</v>
-      </c>
-      <c r="B9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1476,24 +1475,24 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1"/>
     </row>
@@ -1557,46 +1556,46 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
         <v>88</v>
-      </c>
-      <c r="B6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1629,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C2" s="1"/>
     </row>
@@ -1660,46 +1659,46 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" t="s">
         <v>98</v>
-      </c>
-      <c r="B6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>127</v>
+      <c r="B8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" t="s">
         <v>138</v>
+      </c>
+      <c r="C9" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
